--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -675,65 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53258400</v>
+        <v>72475294</v>
       </c>
       <c r="B2" t="n">
-        <v>55511</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102932</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>rastande</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ersträskbäcken, Koler, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754650.6901225173</v>
+        <v>754651</v>
       </c>
       <c r="R2" t="n">
-        <v>7272885.642898775</v>
+        <v>7272886</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -760,22 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-05-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 adulta och 2 1k.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>58751887</v>
+        <v>77427419</v>
       </c>
       <c r="B3" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>102931</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,22 +823,27 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ersträskbäcken, Koler, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754650.6901225173</v>
+        <v>754651</v>
       </c>
       <c r="R3" t="n">
-        <v>7272885.642898775</v>
+        <v>7272886</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -883,22 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-04-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-04-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,66 +902,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>77427419</v>
+        <v>53258400</v>
       </c>
       <c r="B4" t="n">
-        <v>55504</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102931</v>
+        <v>102932</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ersträskbäcken, Koler, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754650.6901225173</v>
+        <v>754651</v>
       </c>
       <c r="R4" t="n">
-        <v>7272885.642898775</v>
+        <v>7272886</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1011,22 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,37 +1014,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322933</v>
+        <v>58751887</v>
       </c>
       <c r="B5" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100045</v>
+        <v>102999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1098,7 +1054,6 @@
           <t>rastande</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ersträskbäcken, Koler, Nb</t>
@@ -1135,12 +1090,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72475294</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77427419</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53258400</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,8 +1139,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58751887</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>